--- a/output/yearly_benthic_cover_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_22_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.01047481038727</v>
+        <v>45.13899244698022</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2364179921479</v>
+        <v>99.79190340553893</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09785198113178</v>
+        <v>87.9138430089248</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94748006490886</v>
+        <v>45.83622568798665</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228897198153388</v>
+        <v>2.228509409223827</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720992160791026</v>
+        <v>5.647494927456369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429657327177962</v>
+        <v>0.7428364697412758</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97889889953947</v>
+        <v>33.94218428898901</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17642370501862</v>
+        <v>34.17047760809869</v>
       </c>
       <c r="I3" t="n">
-        <v>6.60613845542527</v>
+        <v>6.539612369532664</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643535829486226</v>
+        <v>4.642727935882974</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9021480188682</v>
+        <v>12.08615699107518</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91326314473188</v>
+        <v>48.84285547187564</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7628912285089</v>
+        <v>106.7652381509375</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.30351865713705</v>
+        <v>86.96419158926405</v>
       </c>
       <c r="C4" t="n">
-        <v>42.79493989712712</v>
+        <v>42.51965317151813</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191277002818515</v>
+        <v>2.182460925452583</v>
       </c>
       <c r="E4" t="n">
-        <v>6.54388285791947</v>
+        <v>6.440979462617253</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445306666733699</v>
+        <v>0.7443913981120814</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40538980503135</v>
+        <v>33.24082484400624</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24841066697501</v>
+        <v>34.24200431315575</v>
       </c>
       <c r="I4" t="n">
-        <v>5.516710991010768</v>
+        <v>5.461084407719619</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653316666708561</v>
+        <v>4.652446238200509</v>
       </c>
       <c r="K4" t="n">
-        <v>12.69648134286293</v>
+        <v>13.03580841073596</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3250749140259</v>
+        <v>44.26288251859221</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81649615401597</v>
+        <v>99.8183441008463</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.34336938327691</v>
+        <v>85.65571087423039</v>
       </c>
       <c r="C5" t="n">
-        <v>42.69114091844516</v>
+        <v>42.05865986067113</v>
       </c>
       <c r="D5" t="n">
-        <v>2.145157179104791</v>
+        <v>2.117998414205943</v>
       </c>
       <c r="E5" t="n">
-        <v>7.17372585050151</v>
+        <v>7.010564331154584</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458544070016628</v>
+        <v>0.7457120587399826</v>
       </c>
       <c r="G5" t="n">
-        <v>32.70230631220291</v>
+        <v>32.25900335049658</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30930272207649</v>
+        <v>34.3027547020392</v>
       </c>
       <c r="I5" t="n">
-        <v>4.605432868629148</v>
+        <v>4.558977650469218</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661590043760392</v>
+        <v>4.660700367124891</v>
       </c>
       <c r="K5" t="n">
-        <v>13.65663061672308</v>
+        <v>14.3442891257696</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49898649285922</v>
+        <v>43.44535422445594</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84675802802747</v>
+        <v>99.84830321089667</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.18597496529746</v>
+        <v>84.15047231383188</v>
       </c>
       <c r="C6" t="n">
-        <v>42.24929278480769</v>
+        <v>41.26123093454152</v>
       </c>
       <c r="D6" t="n">
-        <v>2.089210357553472</v>
+        <v>2.044044292436681</v>
       </c>
       <c r="E6" t="n">
-        <v>7.627236815291853</v>
+        <v>7.399922219762249</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469761842113541</v>
+        <v>0.7468359741702789</v>
       </c>
       <c r="G6" t="n">
-        <v>31.84941305412992</v>
+        <v>31.1326161700642</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36090447372229</v>
+        <v>34.35445481183284</v>
       </c>
       <c r="I6" t="n">
-        <v>3.843632929067618</v>
+        <v>3.804874007001394</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668601151320963</v>
+        <v>4.667724838564243</v>
       </c>
       <c r="K6" t="n">
-        <v>14.81402503470254</v>
+        <v>15.84952768616812</v>
       </c>
       <c r="L6" t="n">
-        <v>42.8087534896945</v>
+        <v>42.76260311122177</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87207130920474</v>
+        <v>99.87336173193141</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.86908640087402</v>
+        <v>82.49341518736958</v>
       </c>
       <c r="C7" t="n">
-        <v>41.52978575357814</v>
+        <v>40.19481625316575</v>
       </c>
       <c r="D7" t="n">
-        <v>2.025598687330951</v>
+        <v>1.963085196809785</v>
       </c>
       <c r="E7" t="n">
-        <v>7.929523286757789</v>
+        <v>7.635963857967999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479283168844697</v>
+        <v>0.7477940513635247</v>
       </c>
       <c r="G7" t="n">
-        <v>30.87967137510021</v>
+        <v>29.89953699513935</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4047025766856</v>
+        <v>34.39852636272214</v>
       </c>
       <c r="I7" t="n">
-        <v>3.207110177587073</v>
+        <v>3.17479590234475</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674551980527935</v>
+        <v>4.673712821022029</v>
       </c>
       <c r="K7" t="n">
-        <v>16.13091359912595</v>
+        <v>17.50658481263041</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23253306593293</v>
+        <v>42.19290798956491</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89323241863703</v>
+        <v>99.89430905536108</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.69701217907381</v>
+        <v>87.44946701986306</v>
       </c>
       <c r="C8" t="n">
-        <v>43.76372157849958</v>
+        <v>42.55498447838677</v>
       </c>
       <c r="D8" t="n">
-        <v>2.029920478049392</v>
+        <v>1.967310368626397</v>
       </c>
       <c r="E8" t="n">
-        <v>9.718948421179913</v>
+        <v>9.508478538635273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495240869045569</v>
+        <v>0.7494035374701828</v>
       </c>
       <c r="G8" t="n">
-        <v>31.35870229314137</v>
+        <v>30.42138363720155</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47810799760961</v>
+        <v>34.47256272362841</v>
       </c>
       <c r="I8" t="n">
-        <v>5.677283359035488</v>
+        <v>5.646556105112603</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68452554315348</v>
+        <v>4.683772109188642</v>
       </c>
       <c r="K8" t="n">
-        <v>11.30298782092619</v>
+        <v>12.55053298013694</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74445072820774</v>
+        <v>44.70666823961395</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8111601276335</v>
+        <v>99.81218569813767</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.91316624479715</v>
+        <v>85.38883158108862</v>
       </c>
       <c r="C9" t="n">
-        <v>42.86176092264238</v>
+        <v>41.37018454664681</v>
       </c>
       <c r="D9" t="n">
-        <v>1.949457049143011</v>
+        <v>1.873994120091563</v>
       </c>
       <c r="E9" t="n">
-        <v>10.12364676231737</v>
+        <v>9.843146047137392</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508865565254421</v>
+        <v>0.7507826328196121</v>
       </c>
       <c r="G9" t="n">
-        <v>30.11568379076871</v>
+        <v>28.9783935317589</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54078160017033</v>
+        <v>34.53600110970216</v>
       </c>
       <c r="I9" t="n">
-        <v>4.73966950758826</v>
+        <v>4.714122684456424</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693040978284014</v>
+        <v>4.692391455122575</v>
       </c>
       <c r="K9" t="n">
-        <v>13.08683375520286</v>
+        <v>14.61116841891138</v>
       </c>
       <c r="L9" t="n">
-        <v>43.893703006626</v>
+        <v>43.86179825374423</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84229768447123</v>
+        <v>99.84315121930241</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.94244274417443</v>
+        <v>83.1683223376578</v>
       </c>
       <c r="C10" t="n">
-        <v>41.6272380897413</v>
+        <v>39.8805463501067</v>
       </c>
       <c r="D10" t="n">
-        <v>1.861278881953196</v>
+        <v>1.774535582404761</v>
       </c>
       <c r="E10" t="n">
-        <v>10.32504161478883</v>
+        <v>9.976512275253148</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520522082317018</v>
+        <v>0.7519665981599879</v>
       </c>
       <c r="G10" t="n">
-        <v>28.75348614629873</v>
+        <v>27.44042251345037</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59440157865828</v>
+        <v>34.59046351535945</v>
       </c>
       <c r="I10" t="n">
-        <v>3.955856012795544</v>
+        <v>3.934630614530165</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700326301448137</v>
+        <v>4.699791238499923</v>
       </c>
       <c r="K10" t="n">
-        <v>15.05755725582559</v>
+        <v>16.83167766234221</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18354716811123</v>
+        <v>43.15682813520509</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86834251367812</v>
+        <v>99.869052147654</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.7978330727548</v>
+        <v>80.83451381214338</v>
       </c>
       <c r="C11" t="n">
-        <v>40.09667362607445</v>
+        <v>38.15610491799414</v>
       </c>
       <c r="D11" t="n">
-        <v>1.766120694094253</v>
+        <v>1.671123463983192</v>
       </c>
       <c r="E11" t="n">
-        <v>10.34732675238694</v>
+        <v>9.942341436270192</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530516183685223</v>
+        <v>0.7529846989786828</v>
       </c>
       <c r="G11" t="n">
-        <v>27.28345945506064</v>
+        <v>25.84131554110476</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64037444495202</v>
+        <v>34.63729615301941</v>
       </c>
       <c r="I11" t="n">
-        <v>3.300927493089169</v>
+        <v>3.283298150170363</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706572614803266</v>
+        <v>4.706154368616767</v>
       </c>
       <c r="K11" t="n">
-        <v>17.2021669272452</v>
+        <v>19.16548618785664</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59127455743604</v>
+        <v>42.56911359930118</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89011511075569</v>
+        <v>99.89070470515196</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.60994559667023</v>
+        <v>78.5430948584969</v>
       </c>
       <c r="C12" t="n">
-        <v>38.42053319564372</v>
+        <v>36.37235981865847</v>
       </c>
       <c r="D12" t="n">
-        <v>1.669939594303246</v>
+        <v>1.570710888052013</v>
       </c>
       <c r="E12" t="n">
-        <v>10.24280631635301</v>
+        <v>9.80148103496686</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539091771252283</v>
+        <v>0.7538600667437315</v>
       </c>
       <c r="G12" t="n">
-        <v>25.79763057299951</v>
+        <v>24.28859181071806</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6798221477605</v>
+        <v>34.67756307021165</v>
       </c>
       <c r="I12" t="n">
-        <v>2.753905431096057</v>
+        <v>2.739262570656246</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711932357032678</v>
+        <v>4.711625417148322</v>
       </c>
       <c r="K12" t="n">
-        <v>19.39005440332977</v>
+        <v>21.4569051415031</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09771997066293</v>
+        <v>42.07953231344482</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90830756963642</v>
+        <v>99.9087972736064</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.34108870744318</v>
+        <v>76.20525159858697</v>
       </c>
       <c r="C13" t="n">
-        <v>36.57791563698395</v>
+        <v>34.4572536753841</v>
       </c>
       <c r="D13" t="n">
-        <v>1.571001171811164</v>
+        <v>1.469205501137383</v>
       </c>
       <c r="E13" t="n">
-        <v>10.01881448346405</v>
+        <v>9.548904977107876</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546460629967603</v>
+        <v>0.7546135452319818</v>
       </c>
       <c r="G13" t="n">
-        <v>24.26920590324911</v>
+        <v>22.71896946448472</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71371889785097</v>
+        <v>34.71222308067117</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297164294341376</v>
+        <v>2.285000372253956</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716537893729753</v>
+        <v>4.716334657699885</v>
       </c>
       <c r="K13" t="n">
-        <v>21.65891129255683</v>
+        <v>23.79474840141304</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68667569737323</v>
+        <v>41.67190729624018</v>
       </c>
       <c r="M13" t="n">
-        <v>99.923502626914</v>
+        <v>99.92390937303732</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.46336152391913</v>
+        <v>83.16573649583093</v>
       </c>
       <c r="C14" t="n">
-        <v>40.33672586448235</v>
+        <v>38.86374294320179</v>
       </c>
       <c r="D14" t="n">
-        <v>1.572853445174656</v>
+        <v>1.470873209261138</v>
       </c>
       <c r="E14" t="n">
-        <v>12.14331522983952</v>
+        <v>11.98425552963599</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755535820959029</v>
+        <v>0.7554701137233909</v>
       </c>
       <c r="G14" t="n">
-        <v>25.91257998541527</v>
+        <v>24.69725866800133</v>
       </c>
       <c r="H14" t="n">
-        <v>36.36940747956156</v>
+        <v>36.70412593215635</v>
       </c>
       <c r="I14" t="n">
-        <v>2.987570681975182</v>
+        <v>2.832064832281536</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722098880993933</v>
+        <v>4.721688210771192</v>
       </c>
       <c r="K14" t="n">
-        <v>15.53663847608086</v>
+        <v>16.83426350416908</v>
       </c>
       <c r="L14" t="n">
-        <v>44.02716724728328</v>
+        <v>44.20769842678219</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90053158784649</v>
+        <v>99.90570487415305</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.82802349711584</v>
+        <v>82.48282297527979</v>
       </c>
       <c r="C15" t="n">
-        <v>40.1638868270817</v>
+        <v>38.61828633788761</v>
       </c>
       <c r="D15" t="n">
-        <v>1.549170712857531</v>
+        <v>1.445924185324219</v>
       </c>
       <c r="E15" t="n">
-        <v>12.37582274843496</v>
+        <v>12.17469584461538</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562845275859978</v>
+        <v>0.7561913355658038</v>
       </c>
       <c r="G15" t="n">
-        <v>25.52240968866996</v>
+        <v>24.27834254810425</v>
       </c>
       <c r="H15" t="n">
-        <v>36.40544814850603</v>
+        <v>36.73916612348633</v>
       </c>
       <c r="I15" t="n">
-        <v>2.492109373648858</v>
+        <v>2.362307090897533</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726778297412488</v>
+        <v>4.726195847286273</v>
       </c>
       <c r="K15" t="n">
-        <v>16.17197650288418</v>
+        <v>17.5171770247202</v>
       </c>
       <c r="L15" t="n">
-        <v>43.58114859553481</v>
+        <v>43.78586816982882</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91701192550069</v>
+        <v>99.92133153243664</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.64153391507958</v>
+        <v>80.12892577471538</v>
       </c>
       <c r="C16" t="n">
-        <v>38.36332439740788</v>
+        <v>36.62935492011435</v>
       </c>
       <c r="D16" t="n">
-        <v>1.464545133990385</v>
+        <v>1.357229585439152</v>
       </c>
       <c r="E16" t="n">
-        <v>12.04619646289046</v>
+        <v>11.75625355764107</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569263384432149</v>
+        <v>0.7568111076771059</v>
       </c>
       <c r="G16" t="n">
-        <v>24.12821298971209</v>
+        <v>22.78908197688429</v>
       </c>
       <c r="H16" t="n">
-        <v>36.4363431503622</v>
+        <v>36.76927743194081</v>
       </c>
       <c r="I16" t="n">
-        <v>2.078520224411116</v>
+        <v>1.97020269215104</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730789615270094</v>
+        <v>4.730069422981911</v>
       </c>
       <c r="K16" t="n">
-        <v>18.35846608492042</v>
+        <v>19.87107422528461</v>
       </c>
       <c r="L16" t="n">
-        <v>43.20898425729257</v>
+        <v>43.43395121318721</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93077473962087</v>
+        <v>99.93438035858617</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.14304830638579</v>
+        <v>81.972441796273</v>
       </c>
       <c r="C17" t="n">
-        <v>39.47821758758938</v>
+        <v>37.97424019768741</v>
       </c>
       <c r="D17" t="n">
-        <v>1.465755389655209</v>
+        <v>1.358300208371733</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76953384199243</v>
+        <v>12.58513355631104</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575518394043631</v>
+        <v>0.7574081027147941</v>
       </c>
       <c r="G17" t="n">
-        <v>24.51800011779328</v>
+        <v>23.30335353671854</v>
       </c>
       <c r="H17" t="n">
-        <v>36.8363013437828</v>
+        <v>37.29457698439821</v>
       </c>
       <c r="I17" t="n">
-        <v>2.061206777480438</v>
+        <v>1.939868765791219</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73469899627727</v>
+        <v>4.733800641967463</v>
       </c>
       <c r="K17" t="n">
-        <v>16.85695169361422</v>
+        <v>18.02755820372699</v>
       </c>
       <c r="L17" t="n">
-        <v>43.59618055662489</v>
+        <v>43.93359027372103</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93134983782849</v>
+        <v>99.93538867513543</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.02105954851855</v>
+        <v>79.70320070024579</v>
       </c>
       <c r="C18" t="n">
-        <v>37.67513115007256</v>
+        <v>36.0043805255599</v>
       </c>
       <c r="D18" t="n">
-        <v>1.386475762352698</v>
+        <v>1.276409423321166</v>
       </c>
       <c r="E18" t="n">
-        <v>12.36533777302492</v>
+        <v>12.09599485856042</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580875626783224</v>
+        <v>0.7579205128944073</v>
       </c>
       <c r="G18" t="n">
-        <v>23.19187304006935</v>
+        <v>21.89841381597713</v>
       </c>
       <c r="H18" t="n">
-        <v>36.86235113064882</v>
+        <v>37.31980792769374</v>
       </c>
       <c r="I18" t="n">
-        <v>1.718887013004927</v>
+        <v>1.617650956208873</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738047266739517</v>
+        <v>4.737003205590046</v>
       </c>
       <c r="K18" t="n">
-        <v>18.97894045148145</v>
+        <v>20.2967992997542</v>
       </c>
       <c r="L18" t="n">
-        <v>43.28867265462711</v>
+        <v>43.64493493119169</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94274425618111</v>
+        <v>99.94611475650579</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.14986645324697</v>
+        <v>78.80438122457673</v>
       </c>
       <c r="C19" t="n">
-        <v>37.0693153502155</v>
+        <v>35.35459287900194</v>
       </c>
       <c r="D19" t="n">
-        <v>1.354587330341025</v>
+        <v>1.244591877676913</v>
       </c>
       <c r="E19" t="n">
-        <v>12.31981616824533</v>
+        <v>12.01927529800903</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585394396326852</v>
+        <v>0.7583529304566018</v>
       </c>
       <c r="G19" t="n">
-        <v>22.65846849976445</v>
+        <v>21.35254368340347</v>
       </c>
       <c r="H19" t="n">
-        <v>36.88432385224409</v>
+        <v>37.34110005541837</v>
       </c>
       <c r="I19" t="n">
-        <v>1.433259665315112</v>
+        <v>1.348811564258578</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740871497704283</v>
+        <v>4.739705815353761</v>
       </c>
       <c r="K19" t="n">
-        <v>19.85013354675302</v>
+        <v>21.19561877542328</v>
       </c>
       <c r="L19" t="n">
-        <v>43.03280424155911</v>
+        <v>43.40485359679118</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95225313852762</v>
+        <v>99.95506525121641</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.82551985858039</v>
+        <v>76.33480469202092</v>
       </c>
       <c r="C20" t="n">
-        <v>34.9661286857218</v>
+        <v>33.09252219647057</v>
       </c>
       <c r="D20" t="n">
-        <v>1.268578388279323</v>
+        <v>1.156368764959536</v>
       </c>
       <c r="E20" t="n">
-        <v>11.73674044853531</v>
+        <v>11.35471380157504</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589276800462974</v>
+        <v>0.7587253313937951</v>
       </c>
       <c r="G20" t="n">
-        <v>21.21977875215511</v>
+        <v>19.83896489346327</v>
       </c>
       <c r="H20" t="n">
-        <v>36.90320221821954</v>
+        <v>37.35943698021681</v>
       </c>
       <c r="I20" t="n">
-        <v>1.194994371055443</v>
+        <v>1.124561599201245</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74329800028936</v>
+        <v>4.74203332121122</v>
       </c>
       <c r="K20" t="n">
-        <v>22.1744801414196</v>
+        <v>23.66519530797909</v>
       </c>
       <c r="L20" t="n">
-        <v>42.81957840437763</v>
+        <v>43.20481550765427</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96018723151903</v>
+        <v>99.96253301210393</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.02999024076472</v>
+        <v>82.15739324627606</v>
       </c>
       <c r="C21" t="n">
-        <v>38.11533347060983</v>
+        <v>36.74855564081763</v>
       </c>
       <c r="D21" t="n">
-        <v>1.269491739425598</v>
+        <v>1.157103838440454</v>
       </c>
       <c r="E21" t="n">
-        <v>13.46142185192356</v>
+        <v>13.31354326265117</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759474092844209</v>
+        <v>0.7592076333093329</v>
       </c>
       <c r="G21" t="n">
-        <v>22.65238806656064</v>
+        <v>21.54206100531605</v>
       </c>
       <c r="H21" t="n">
-        <v>38.34710328481995</v>
+        <v>39.07367039947047</v>
       </c>
       <c r="I21" t="n">
-        <v>1.793398124914442</v>
+        <v>1.566759398905244</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746713080276307</v>
+        <v>4.745047708183331</v>
       </c>
       <c r="K21" t="n">
-        <v>16.97000975923529</v>
+        <v>17.84260675372393</v>
       </c>
       <c r="L21" t="n">
-        <v>44.85491984205491</v>
+        <v>45.35664546934203</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94026307190002</v>
+        <v>99.94780786388361</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_22_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.13899244698022</v>
+        <v>45.71336200012696</v>
       </c>
       <c r="M2" t="n">
-        <v>99.79190340553893</v>
+        <v>98.75224467539414</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9138430089248</v>
+        <v>88.06395223290417</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83622568798665</v>
+        <v>45.92762442212124</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228509409223827</v>
+        <v>2.228825382209383</v>
       </c>
       <c r="E3" t="n">
-        <v>5.647494927456369</v>
+        <v>5.707813632600345</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428364697412758</v>
+        <v>0.7429417940697943</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94218428898901</v>
+        <v>33.97235879803854</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17047760809869</v>
+        <v>34.17532252721053</v>
       </c>
       <c r="I3" t="n">
-        <v>6.539612369532664</v>
+        <v>6.593303885839341</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642727935882974</v>
+        <v>4.643386212936214</v>
       </c>
       <c r="K3" t="n">
-        <v>12.08615699107518</v>
+        <v>11.93604776709584</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84285547187564</v>
+        <v>48.89967207495121</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652381509375</v>
+        <v>106.7633442641683</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.96419158926405</v>
+        <v>87.22991482954835</v>
       </c>
       <c r="C4" t="n">
-        <v>42.51965317151813</v>
+        <v>42.73363885437328</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182460925452583</v>
+        <v>2.189065332434858</v>
       </c>
       <c r="E4" t="n">
-        <v>6.440979462617253</v>
+        <v>6.523655229219763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443913981120814</v>
+        <v>0.7445049515535086</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24082484400624</v>
+        <v>33.36632537453676</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24200431315575</v>
+        <v>34.24722777146139</v>
       </c>
       <c r="I4" t="n">
-        <v>5.461084407719619</v>
+        <v>5.505980223132656</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652446238200509</v>
+        <v>4.653155947209428</v>
       </c>
       <c r="K4" t="n">
-        <v>13.03580841073596</v>
+        <v>12.77008517045165</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26288251859221</v>
+        <v>44.31312864501287</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8183441008463</v>
+        <v>99.8168526698378</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.65571087423039</v>
+        <v>86.18818810217341</v>
       </c>
       <c r="C5" t="n">
-        <v>42.05865986067113</v>
+        <v>42.54654363580503</v>
       </c>
       <c r="D5" t="n">
-        <v>2.117998414205943</v>
+        <v>2.138667039612729</v>
       </c>
       <c r="E5" t="n">
-        <v>7.010564331154584</v>
+        <v>7.139541687478456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457120587399826</v>
+        <v>0.7458284497111716</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25900335049658</v>
+        <v>32.59814097560248</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3027547020392</v>
+        <v>34.30810868671389</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558977650469218</v>
+        <v>4.596473452359861</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660700367124891</v>
+        <v>4.661427810694822</v>
       </c>
       <c r="K5" t="n">
-        <v>14.3442891257696</v>
+        <v>13.81181189782659</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44535422445594</v>
+        <v>43.48870057128136</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84830321089667</v>
+        <v>99.84705610491298</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.15047231383188</v>
+        <v>84.87053105081571</v>
       </c>
       <c r="C6" t="n">
-        <v>41.26123093454152</v>
+        <v>41.94292019165268</v>
       </c>
       <c r="D6" t="n">
-        <v>2.044044292436681</v>
+        <v>2.074493859861675</v>
       </c>
       <c r="E6" t="n">
-        <v>7.399922219762249</v>
+        <v>7.564672425731647</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468359741702789</v>
+        <v>0.7469521697586264</v>
       </c>
       <c r="G6" t="n">
-        <v>31.1326161700642</v>
+        <v>31.61999602754346</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35445481183284</v>
+        <v>34.35979980889681</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804874007001394</v>
+        <v>3.836165698032073</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667724838564243</v>
+        <v>4.668451060991416</v>
       </c>
       <c r="K6" t="n">
-        <v>15.84952768616812</v>
+        <v>15.12946894918428</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76260311122177</v>
+        <v>42.79993104104193</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87336173193141</v>
+        <v>99.87232018187889</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.49341518736958</v>
+        <v>83.38834481834296</v>
       </c>
       <c r="C7" t="n">
-        <v>40.19481625316575</v>
+        <v>41.05672904181597</v>
       </c>
       <c r="D7" t="n">
-        <v>1.963085196809785</v>
+        <v>2.002529128942164</v>
       </c>
       <c r="E7" t="n">
-        <v>7.635963857967999</v>
+        <v>7.835734491237959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477940513635247</v>
+        <v>0.7479079050585</v>
       </c>
       <c r="G7" t="n">
-        <v>29.89953699513935</v>
+        <v>30.52309015096984</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39852636272214</v>
+        <v>34.403763632691</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17479590234475</v>
+        <v>3.200895102827869</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673712821022029</v>
+        <v>4.674424406615625</v>
       </c>
       <c r="K7" t="n">
-        <v>17.50658481263041</v>
+        <v>16.61165518165706</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19290798956491</v>
+        <v>42.22505561824828</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89430905536108</v>
+        <v>99.89343984172132</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.44946701986306</v>
+        <v>88.28600094867905</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55498447838677</v>
+        <v>43.42817918284515</v>
       </c>
       <c r="D8" t="n">
-        <v>1.967310368626397</v>
+        <v>2.00676696078457</v>
       </c>
       <c r="E8" t="n">
-        <v>9.508478538635273</v>
+        <v>9.712923960780797</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494035374701828</v>
+        <v>0.7494906575335757</v>
       </c>
       <c r="G8" t="n">
-        <v>30.42138363720155</v>
+        <v>31.05090204495452</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47256272362841</v>
+        <v>34.47657024654448</v>
       </c>
       <c r="I8" t="n">
-        <v>5.646556105112603</v>
+        <v>5.605030468496271</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683772109188642</v>
+        <v>4.684316609584848</v>
       </c>
       <c r="K8" t="n">
-        <v>12.55053298013694</v>
+        <v>11.71399905132094</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70666823961395</v>
+        <v>44.67138196820402</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81218569813767</v>
+        <v>99.8135602023701</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.38883158108862</v>
+        <v>86.21142821893837</v>
       </c>
       <c r="C9" t="n">
-        <v>41.37018454664681</v>
+        <v>42.22398734827058</v>
       </c>
       <c r="D9" t="n">
-        <v>1.873994120091563</v>
+        <v>1.912884039636819</v>
       </c>
       <c r="E9" t="n">
-        <v>9.843146047137392</v>
+        <v>10.03840748481268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507826328196121</v>
+        <v>0.7508466644130671</v>
       </c>
       <c r="G9" t="n">
-        <v>28.9783935317589</v>
+        <v>29.59824239626601</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53600110970216</v>
+        <v>34.53894656300108</v>
       </c>
       <c r="I9" t="n">
-        <v>4.714122684456424</v>
+        <v>4.67930941822703</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692391455122575</v>
+        <v>4.69279165258167</v>
       </c>
       <c r="K9" t="n">
-        <v>14.61116841891138</v>
+        <v>13.78857178106163</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86179825374423</v>
+        <v>43.83174557987622</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84315121930241</v>
+        <v>99.84430470920843</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.1683223376578</v>
+        <v>84.01342106267757</v>
       </c>
       <c r="C10" t="n">
-        <v>39.8805463501067</v>
+        <v>40.75227751473265</v>
       </c>
       <c r="D10" t="n">
-        <v>1.774535582404761</v>
+        <v>1.814498068039464</v>
       </c>
       <c r="E10" t="n">
-        <v>9.976512275253148</v>
+        <v>10.17301002715256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519665981599879</v>
+        <v>0.7520101319905338</v>
       </c>
       <c r="G10" t="n">
-        <v>27.44042251345037</v>
+        <v>28.0759066062285</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59046351535945</v>
+        <v>34.59246607156455</v>
       </c>
       <c r="I10" t="n">
-        <v>3.934630614530165</v>
+        <v>3.905466832761113</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699791238499923</v>
+        <v>4.700063324940837</v>
       </c>
       <c r="K10" t="n">
-        <v>16.83167766234221</v>
+        <v>15.98657893732242</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15682813520509</v>
+        <v>43.13116273077194</v>
       </c>
       <c r="M10" t="n">
-        <v>99.869052147654</v>
+        <v>99.87001918282702</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.83451381214338</v>
+        <v>81.62753771272359</v>
       </c>
       <c r="C11" t="n">
-        <v>38.15610491799414</v>
+        <v>38.97196743245169</v>
       </c>
       <c r="D11" t="n">
-        <v>1.671123463983192</v>
+        <v>1.708710784306392</v>
       </c>
       <c r="E11" t="n">
-        <v>9.942341436270192</v>
+        <v>10.12305987660333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529846989786828</v>
+        <v>0.7530109037043214</v>
       </c>
       <c r="G11" t="n">
-        <v>25.84131554110476</v>
+        <v>26.43904958745777</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63729615301941</v>
+        <v>34.63850157039878</v>
       </c>
       <c r="I11" t="n">
-        <v>3.283298150170363</v>
+        <v>3.258886842100995</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706154368616767</v>
+        <v>4.706318148152009</v>
       </c>
       <c r="K11" t="n">
-        <v>19.16548618785664</v>
+        <v>18.3724622872764</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56911359930118</v>
+        <v>42.54708509047298</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89070470515196</v>
+        <v>99.89151481020107</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.5430948584969</v>
+        <v>79.0748623818691</v>
       </c>
       <c r="C12" t="n">
-        <v>36.37235981865847</v>
+        <v>36.92377899373133</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570710888052013</v>
+        <v>1.596567000664233</v>
       </c>
       <c r="E12" t="n">
-        <v>9.80148103496686</v>
+        <v>9.911818898339472</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538600667437315</v>
+        <v>0.753873936031724</v>
       </c>
       <c r="G12" t="n">
-        <v>24.28859181071806</v>
+        <v>24.70383782203092</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67756307021165</v>
+        <v>34.6782010574593</v>
       </c>
       <c r="I12" t="n">
-        <v>2.739262570656246</v>
+        <v>2.718851567145169</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711625417148322</v>
+        <v>4.711712100198276</v>
       </c>
       <c r="K12" t="n">
-        <v>21.4569051415031</v>
+        <v>20.92513761813091</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07953231344482</v>
+        <v>42.06055875363495</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9087972736064</v>
+        <v>99.90947536549719</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.20525159858697</v>
+        <v>76.53302850402251</v>
       </c>
       <c r="C13" t="n">
-        <v>34.4572536753841</v>
+        <v>34.80188205243438</v>
       </c>
       <c r="D13" t="n">
-        <v>1.469205501137383</v>
+        <v>1.485966014786091</v>
       </c>
       <c r="E13" t="n">
-        <v>9.548904977107876</v>
+        <v>9.603176330391799</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546135452319818</v>
+        <v>0.7546186021688327</v>
       </c>
       <c r="G13" t="n">
-        <v>22.71896946448472</v>
+        <v>22.9924979177528</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71222308067117</v>
+        <v>34.7124556997663</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285000372253956</v>
+        <v>2.267947675601483</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716334657699885</v>
+        <v>4.716366263555205</v>
       </c>
       <c r="K13" t="n">
-        <v>23.79474840141304</v>
+        <v>23.46697149597749</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67190729624018</v>
+        <v>41.65562279694522</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92390937303732</v>
+        <v>99.92447634535709</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.16573649583093</v>
+        <v>83.54873591021169</v>
       </c>
       <c r="C14" t="n">
-        <v>38.86374294320179</v>
+        <v>39.04894815435184</v>
       </c>
       <c r="D14" t="n">
-        <v>1.470873209261138</v>
+        <v>1.487818413147156</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98425552963599</v>
+        <v>11.98449667908514</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554701137233909</v>
+        <v>0.7555593062279951</v>
       </c>
       <c r="G14" t="n">
-        <v>24.69725866800133</v>
+        <v>24.86975199404953</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70412593215635</v>
+        <v>36.60431982122632</v>
       </c>
       <c r="I14" t="n">
-        <v>2.832064832281536</v>
+        <v>3.124544032550584</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721688210771192</v>
+        <v>4.722245663924969</v>
       </c>
       <c r="K14" t="n">
-        <v>16.83426350416908</v>
+        <v>16.45126408978831</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20769842678219</v>
+        <v>44.39576596119626</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90570487415305</v>
+        <v>99.89597820533641</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.48282297527979</v>
+        <v>82.69335877045555</v>
       </c>
       <c r="C15" t="n">
-        <v>38.61828633788761</v>
+        <v>38.67225725847091</v>
       </c>
       <c r="D15" t="n">
-        <v>1.445924185324219</v>
+        <v>1.455693803010566</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17469584461538</v>
+        <v>12.16411137321648</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561913355658038</v>
+        <v>0.7563531556623404</v>
       </c>
       <c r="G15" t="n">
-        <v>24.27834254810425</v>
+        <v>24.33673101104721</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73916612348633</v>
+        <v>36.64673976980798</v>
       </c>
       <c r="I15" t="n">
-        <v>2.362307090897533</v>
+        <v>2.606522434821328</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726195847286273</v>
+        <v>4.727207222889628</v>
       </c>
       <c r="K15" t="n">
-        <v>17.5171770247202</v>
+        <v>17.30664122954447</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78586816982882</v>
+        <v>43.93430862219155</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92133153243664</v>
+        <v>99.91320711020693</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.12892577471538</v>
+        <v>80.16856874701288</v>
       </c>
       <c r="C16" t="n">
-        <v>36.62935492011435</v>
+        <v>36.55011632433024</v>
       </c>
       <c r="D16" t="n">
-        <v>1.357229585439152</v>
+        <v>1.360092425140015</v>
       </c>
       <c r="E16" t="n">
-        <v>11.75625355764107</v>
+        <v>11.7275885797621</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568111076771059</v>
+        <v>0.7570368655573856</v>
       </c>
       <c r="G16" t="n">
-        <v>22.78908197688429</v>
+        <v>22.73843814704702</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76927743194081</v>
+        <v>36.67986680631756</v>
       </c>
       <c r="I16" t="n">
-        <v>1.97020269215104</v>
+        <v>2.174065513455128</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730069422981911</v>
+        <v>4.73148040973366</v>
       </c>
       <c r="K16" t="n">
-        <v>19.87107422528461</v>
+        <v>19.83143125298712</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43395121318721</v>
+        <v>43.54604902171538</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93438035858617</v>
+        <v>99.92759659903274</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.972441796273</v>
+        <v>81.9207036922592</v>
       </c>
       <c r="C17" t="n">
-        <v>37.97424019768741</v>
+        <v>37.81422086212557</v>
       </c>
       <c r="D17" t="n">
-        <v>1.358300208371733</v>
+        <v>1.361304968759879</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58513355631104</v>
+        <v>12.53670905112293</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574081027147941</v>
+        <v>0.7577117757358164</v>
       </c>
       <c r="G17" t="n">
-        <v>23.30335353671854</v>
+        <v>23.19220703445779</v>
       </c>
       <c r="H17" t="n">
-        <v>37.29457698439821</v>
+        <v>37.14606469491981</v>
       </c>
       <c r="I17" t="n">
-        <v>1.939868765791219</v>
+        <v>2.191007568914129</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733800641967463</v>
+        <v>4.735698598348852</v>
       </c>
       <c r="K17" t="n">
-        <v>18.02755820372699</v>
+        <v>18.0792963077408</v>
       </c>
       <c r="L17" t="n">
-        <v>43.93359027372103</v>
+        <v>44.03351429708896</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93538867513543</v>
+        <v>99.92703146695533</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.70320070024579</v>
+        <v>79.42702525356412</v>
       </c>
       <c r="C18" t="n">
-        <v>36.0043805255599</v>
+        <v>35.65856099817498</v>
       </c>
       <c r="D18" t="n">
-        <v>1.276409423321166</v>
+        <v>1.270754381212531</v>
       </c>
       <c r="E18" t="n">
-        <v>12.09599485856042</v>
+        <v>12.00733861344541</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579205128944073</v>
+        <v>0.758292821078007</v>
       </c>
       <c r="G18" t="n">
-        <v>21.89841381597713</v>
+        <v>21.64951967072693</v>
       </c>
       <c r="H18" t="n">
-        <v>37.31980792769374</v>
+        <v>37.1745498637701</v>
       </c>
       <c r="I18" t="n">
-        <v>1.617650956208873</v>
+        <v>1.827239771593608</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737003205590046</v>
+        <v>4.739330131737543</v>
       </c>
       <c r="K18" t="n">
-        <v>20.2967992997542</v>
+        <v>20.57297474643587</v>
       </c>
       <c r="L18" t="n">
-        <v>43.64493493119169</v>
+        <v>43.70760293403043</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94611475650579</v>
+        <v>99.93913867864129</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.80438122457673</v>
+        <v>78.4611131397868</v>
       </c>
       <c r="C19" t="n">
-        <v>35.35459287900194</v>
+        <v>34.97377667429579</v>
       </c>
       <c r="D19" t="n">
-        <v>1.244591877676913</v>
+        <v>1.236411907016898</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01927529800903</v>
+        <v>11.93678468353778</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583529304566018</v>
+        <v>0.7587836798481004</v>
       </c>
       <c r="G19" t="n">
-        <v>21.35254368340347</v>
+        <v>21.06443565950334</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34110005541837</v>
+        <v>37.19861372580029</v>
       </c>
       <c r="I19" t="n">
-        <v>1.348811564258578</v>
+        <v>1.523685485029767</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739705815353761</v>
+        <v>4.742397999050627</v>
       </c>
       <c r="K19" t="n">
-        <v>21.19561877542328</v>
+        <v>21.53888686021318</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40485359679118</v>
+        <v>43.43657980516899</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95506525121641</v>
+        <v>99.94924333967796</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.33480469202092</v>
+        <v>75.73286572211606</v>
       </c>
       <c r="C20" t="n">
-        <v>33.09252219647057</v>
+        <v>32.47979149626727</v>
       </c>
       <c r="D20" t="n">
-        <v>1.156368764959536</v>
+        <v>1.138523924266779</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35471380157504</v>
+        <v>11.20347867143328</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587253313937951</v>
+        <v>0.7592079761054051</v>
       </c>
       <c r="G20" t="n">
-        <v>19.83896489346327</v>
+        <v>19.39674295711474</v>
       </c>
       <c r="H20" t="n">
-        <v>37.35943698021681</v>
+        <v>37.21941442697502</v>
       </c>
       <c r="I20" t="n">
-        <v>1.124561599201245</v>
+        <v>1.270447915562058</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74203332121122</v>
+        <v>4.745049850658781</v>
       </c>
       <c r="K20" t="n">
-        <v>23.66519530797909</v>
+        <v>24.26713427788393</v>
       </c>
       <c r="L20" t="n">
-        <v>43.20481550765427</v>
+        <v>43.21074962904239</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96253301210393</v>
+        <v>99.9576754031936</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.15739324627606</v>
+        <v>81.81902408253035</v>
       </c>
       <c r="C21" t="n">
-        <v>36.74855564081763</v>
+        <v>36.1863253331972</v>
       </c>
       <c r="D21" t="n">
-        <v>1.157103838440454</v>
+        <v>1.139415214725765</v>
       </c>
       <c r="E21" t="n">
-        <v>13.31354326265117</v>
+        <v>13.21800842286077</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592076333093329</v>
+        <v>0.7598023200722431</v>
       </c>
       <c r="G21" t="n">
-        <v>21.54206100531605</v>
+        <v>21.09742774512979</v>
       </c>
       <c r="H21" t="n">
-        <v>39.07367039947047</v>
+        <v>38.93405164646397</v>
       </c>
       <c r="I21" t="n">
-        <v>1.566759398905244</v>
+        <v>1.921554232826299</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745047708183331</v>
+        <v>4.748764500451519</v>
       </c>
       <c r="K21" t="n">
-        <v>17.84260675372393</v>
+        <v>18.18097591746964</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35664546934203</v>
+        <v>45.56869704513804</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94780786388361</v>
+        <v>99.93599829580488</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_22_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_22_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.71336200012696</v>
+        <v>44.6033745468039</v>
       </c>
       <c r="M2" t="n">
-        <v>98.75224467539414</v>
+        <v>93.28775833795254</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06395223290417</v>
+        <v>81.55007980265448</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92762442212124</v>
+        <v>43.30563535821005</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228825382209383</v>
+        <v>2.184418388781029</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707813632600345</v>
+        <v>4.15297827585227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429417940697943</v>
+        <v>0.7376845841527991</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97235879803854</v>
+        <v>32.85729326458132</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17532252721053</v>
+        <v>33.93349087102875</v>
       </c>
       <c r="I3" t="n">
-        <v>6.593303885839341</v>
+        <v>3.07368576730333</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643386212936214</v>
+        <v>4.610528650954994</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93604776709584</v>
+        <v>18.44992019734551</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89967207495121</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7633442641683</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22991482954835</v>
+        <v>88.65805143740702</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73363885437328</v>
+        <v>42.86056064263587</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189065332434858</v>
+        <v>2.190198677506306</v>
       </c>
       <c r="E4" t="n">
-        <v>6.523655229219763</v>
+        <v>6.512260846015934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445049515535086</v>
+        <v>0.7396366048400853</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36632537453676</v>
+        <v>33.53187979072153</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24722777146139</v>
+        <v>34.02328382264391</v>
       </c>
       <c r="I4" t="n">
-        <v>5.505980223132656</v>
+        <v>7.038062915428737</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653155947209428</v>
+        <v>4.622728780250532</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77008517045165</v>
+        <v>11.34194856259294</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31312864501287</v>
+        <v>45.56350785048772</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8168526698378</v>
+        <v>99.76601705571655</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.18818810217341</v>
+        <v>87.6115434088733</v>
       </c>
       <c r="C5" t="n">
-        <v>42.54654363580503</v>
+        <v>42.90497662880407</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138667039612729</v>
+        <v>2.140705509700267</v>
       </c>
       <c r="E5" t="n">
-        <v>7.139541687478456</v>
+        <v>7.344794465306471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458284497111716</v>
+        <v>0.7412907663203449</v>
       </c>
       <c r="G5" t="n">
-        <v>32.59814097560248</v>
+        <v>32.77414079179943</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30810868671389</v>
+        <v>34.09937525073585</v>
       </c>
       <c r="I5" t="n">
-        <v>4.596473452359861</v>
+        <v>5.878169335508771</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661427810694822</v>
+        <v>4.633067289502154</v>
       </c>
       <c r="K5" t="n">
-        <v>13.81181189782659</v>
+        <v>12.38845659112671</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48870057128136</v>
+        <v>44.51106503241839</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84705610491298</v>
+        <v>99.80449825234918</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.87053105081571</v>
+        <v>86.43778881267104</v>
       </c>
       <c r="C6" t="n">
-        <v>41.94292019165268</v>
+        <v>42.64358934463382</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074493859861675</v>
+        <v>2.085186718877336</v>
       </c>
       <c r="E6" t="n">
-        <v>7.564672425731647</v>
+        <v>7.97226615949037</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469521697586264</v>
+        <v>0.7426937276471164</v>
       </c>
       <c r="G6" t="n">
-        <v>31.61999602754346</v>
+        <v>31.92414967495685</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35979980889681</v>
+        <v>34.16391147176734</v>
       </c>
       <c r="I6" t="n">
-        <v>3.836165698032073</v>
+        <v>4.907745262137548</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668451060991416</v>
+        <v>4.641835797794476</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12946894918428</v>
+        <v>13.56221118732896</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79993104104193</v>
+        <v>43.63091698649532</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87232018187889</v>
+        <v>99.8367175184581</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.38834481834296</v>
+        <v>84.95126145323316</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05672904181597</v>
+        <v>41.91940020794176</v>
       </c>
       <c r="D7" t="n">
-        <v>2.002529128942164</v>
+        <v>2.014585225606542</v>
       </c>
       <c r="E7" t="n">
-        <v>7.835734491237959</v>
+        <v>8.38506332404029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479079050585</v>
+        <v>0.7438874874013712</v>
       </c>
       <c r="G7" t="n">
-        <v>30.52309015096984</v>
+        <v>30.84324281033525</v>
       </c>
       <c r="H7" t="n">
-        <v>34.403763632691</v>
+        <v>34.21882442046306</v>
       </c>
       <c r="I7" t="n">
-        <v>3.200895102827869</v>
+        <v>4.096361389128058</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674424406615625</v>
+        <v>4.649296796258569</v>
       </c>
       <c r="K7" t="n">
-        <v>16.61165518165706</v>
+        <v>15.04873854676686</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22505561824828</v>
+        <v>42.89553498800978</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89343984172132</v>
+        <v>99.86367374271839</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.28600094867905</v>
+        <v>83.39305787742916</v>
       </c>
       <c r="C8" t="n">
-        <v>43.42817918284515</v>
+        <v>40.99751435340283</v>
       </c>
       <c r="D8" t="n">
-        <v>2.00676696078457</v>
+        <v>1.941120505249102</v>
       </c>
       <c r="E8" t="n">
-        <v>9.712923960780797</v>
+        <v>8.649006490211766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494906575335757</v>
+        <v>0.7449038907962416</v>
       </c>
       <c r="G8" t="n">
-        <v>31.05090204495452</v>
+        <v>29.71850002001934</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47657024654448</v>
+        <v>34.2655789766271</v>
       </c>
       <c r="I8" t="n">
-        <v>5.605030468496271</v>
+        <v>3.418298677049104</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684316609584848</v>
+        <v>4.655649317476509</v>
       </c>
       <c r="K8" t="n">
-        <v>11.71399905132094</v>
+        <v>16.60694212257082</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67138196820402</v>
+        <v>42.28175570766168</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8135602023701</v>
+        <v>99.88621218363534</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.21142821893837</v>
+        <v>81.66091229657549</v>
       </c>
       <c r="C9" t="n">
-        <v>42.22398734827058</v>
+        <v>39.79614903056848</v>
       </c>
       <c r="D9" t="n">
-        <v>1.912884039636819</v>
+        <v>1.859869115196082</v>
       </c>
       <c r="E9" t="n">
-        <v>10.03840748481268</v>
+        <v>8.762292907470009</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508466644130671</v>
+        <v>0.7457710499226688</v>
       </c>
       <c r="G9" t="n">
-        <v>29.59824239626601</v>
+        <v>28.4745435369532</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53894656300108</v>
+        <v>34.30546829644275</v>
       </c>
       <c r="I9" t="n">
-        <v>4.67930941822703</v>
+        <v>2.851898328574106</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69279165258167</v>
+        <v>4.661069062016678</v>
       </c>
       <c r="K9" t="n">
-        <v>13.78857178106163</v>
+        <v>18.3390877034245</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83174557987622</v>
+        <v>41.76981052497786</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84430470920843</v>
+        <v>99.90504725897085</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.01342106267757</v>
+        <v>86.12645195239028</v>
       </c>
       <c r="C10" t="n">
-        <v>40.75227751473265</v>
+        <v>42.85966547459664</v>
       </c>
       <c r="D10" t="n">
-        <v>1.814498068039464</v>
+        <v>1.8619867783178</v>
       </c>
       <c r="E10" t="n">
-        <v>10.17301002715256</v>
+        <v>10.52774267632397</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520101319905338</v>
+        <v>0.7466201913148036</v>
       </c>
       <c r="G10" t="n">
-        <v>28.0759066062285</v>
+        <v>29.77211621585181</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59246607156455</v>
+        <v>35.60968011689589</v>
       </c>
       <c r="I10" t="n">
-        <v>3.905466832761113</v>
+        <v>2.941929777968492</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700063324940837</v>
+        <v>4.666376195717521</v>
       </c>
       <c r="K10" t="n">
-        <v>15.98657893732242</v>
+        <v>13.87354804760971</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13116273077194</v>
+        <v>43.16883368176533</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87001918282702</v>
+        <v>99.90204720397168</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.62753771272359</v>
+        <v>85.97148307727494</v>
       </c>
       <c r="C11" t="n">
-        <v>38.97196743245169</v>
+        <v>43.10039059279376</v>
       </c>
       <c r="D11" t="n">
-        <v>1.708710784306392</v>
+        <v>1.852379621700569</v>
       </c>
       <c r="E11" t="n">
-        <v>10.12305987660333</v>
+        <v>10.90675694951894</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530109037043214</v>
+        <v>0.7473430816424209</v>
       </c>
       <c r="G11" t="n">
-        <v>26.43904958745777</v>
+        <v>29.63564146883863</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63850157039878</v>
+        <v>35.66129627038343</v>
       </c>
       <c r="I11" t="n">
-        <v>3.258886842100995</v>
+        <v>2.497171424925827</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706318148152009</v>
+        <v>4.670894260265129</v>
       </c>
       <c r="K11" t="n">
-        <v>18.3724622872764</v>
+        <v>14.02851692272508</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54708509047298</v>
+        <v>42.7879339524842</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89151481020107</v>
+        <v>99.91684146800303</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.0748623818691</v>
+        <v>84.21652069864037</v>
       </c>
       <c r="C12" t="n">
-        <v>36.92377899373133</v>
+        <v>41.73398810763904</v>
       </c>
       <c r="D12" t="n">
-        <v>1.596567000664233</v>
+        <v>1.777162812680385</v>
       </c>
       <c r="E12" t="n">
-        <v>9.911818898339472</v>
+        <v>10.81099785130831</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753873936031724</v>
+        <v>0.7479591465032254</v>
       </c>
       <c r="G12" t="n">
-        <v>24.70383782203092</v>
+        <v>28.43227129652705</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6782010574593</v>
+        <v>35.69069330644702</v>
       </c>
       <c r="I12" t="n">
-        <v>2.718851567145169</v>
+        <v>2.082691619529209</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711712100198276</v>
+        <v>4.674744665645156</v>
       </c>
       <c r="K12" t="n">
-        <v>20.92513761813091</v>
+        <v>15.78347930135963</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06055875363495</v>
+        <v>42.41316671808675</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90947536549719</v>
+        <v>99.93063412708541</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.53302850402251</v>
+        <v>85.3407887171127</v>
       </c>
       <c r="C13" t="n">
-        <v>34.80188205243438</v>
+        <v>42.68187329329862</v>
       </c>
       <c r="D13" t="n">
-        <v>1.485966014786091</v>
+        <v>1.778505888772141</v>
       </c>
       <c r="E13" t="n">
-        <v>9.603176330391799</v>
+        <v>11.43749343237448</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546186021688327</v>
+        <v>0.7485244104397151</v>
       </c>
       <c r="G13" t="n">
-        <v>22.9924979177528</v>
+        <v>28.74960603431151</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7124556997663</v>
+        <v>36.0135135366106</v>
       </c>
       <c r="I13" t="n">
-        <v>2.267947675601483</v>
+        <v>1.934867849356034</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716366263555205</v>
+        <v>4.678277565248217</v>
       </c>
       <c r="K13" t="n">
-        <v>23.46697149597749</v>
+        <v>14.65921128288731</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65562279694522</v>
+        <v>42.59446853403925</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92447634535709</v>
+        <v>99.93555311022517</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.54873591021169</v>
+        <v>83.48480449971115</v>
       </c>
       <c r="C14" t="n">
-        <v>39.04894815435184</v>
+        <v>41.12687719424019</v>
       </c>
       <c r="D14" t="n">
-        <v>1.487818413147156</v>
+        <v>1.700944165000359</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98449667908514</v>
+        <v>11.20760214853933</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555593062279951</v>
+        <v>0.7490066102370274</v>
       </c>
       <c r="G14" t="n">
-        <v>24.86975199404953</v>
+        <v>27.49581822519702</v>
       </c>
       <c r="H14" t="n">
-        <v>36.60431982122632</v>
+        <v>36.03671345993395</v>
       </c>
       <c r="I14" t="n">
-        <v>3.124544032550584</v>
+        <v>1.613428576822043</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722245663924969</v>
+        <v>4.681291313981419</v>
       </c>
       <c r="K14" t="n">
-        <v>16.45126408978831</v>
+        <v>16.51519550028886</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39576596119626</v>
+        <v>42.30418097632217</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89597820533641</v>
+        <v>99.94625367085121</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.69335877045555</v>
+        <v>82.67738573530744</v>
       </c>
       <c r="C15" t="n">
-        <v>38.67225725847091</v>
+        <v>40.54953043194932</v>
       </c>
       <c r="D15" t="n">
-        <v>1.455693803010566</v>
+        <v>1.666867676175078</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16411137321648</v>
+        <v>11.21059094077462</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563531556623404</v>
+        <v>0.7494188494064568</v>
       </c>
       <c r="G15" t="n">
-        <v>24.33673101104721</v>
+        <v>26.94497066548733</v>
       </c>
       <c r="H15" t="n">
-        <v>36.64673976980798</v>
+        <v>36.05654739013249</v>
       </c>
       <c r="I15" t="n">
-        <v>2.606522434821328</v>
+        <v>1.36512240454109</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727207222889628</v>
+        <v>4.683867808790352</v>
       </c>
       <c r="K15" t="n">
-        <v>17.30664122954447</v>
+        <v>17.32261426469257</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93430862219155</v>
+        <v>42.08237625402126</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91320711020693</v>
+        <v>99.95452095066315</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.16856874701288</v>
+        <v>80.39440017142077</v>
       </c>
       <c r="C16" t="n">
-        <v>36.55011632433024</v>
+        <v>38.47846290192086</v>
       </c>
       <c r="D16" t="n">
-        <v>1.360092425140015</v>
+        <v>1.572049085297461</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7275885797621</v>
+        <v>10.76257419627014</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570368655573856</v>
+        <v>0.7497724987050358</v>
       </c>
       <c r="G16" t="n">
-        <v>22.73843814704702</v>
+        <v>25.41222503351079</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67986680631756</v>
+        <v>36.07356240477191</v>
       </c>
       <c r="I16" t="n">
-        <v>2.174065513455128</v>
+        <v>1.138138835958959</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73148040973366</v>
+        <v>4.686078116906471</v>
       </c>
       <c r="K16" t="n">
-        <v>19.83143125298712</v>
+        <v>19.60559982857923</v>
       </c>
       <c r="L16" t="n">
-        <v>43.54604902171538</v>
+        <v>41.87801720270709</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92759659903274</v>
+        <v>99.96207993320719</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.9207036922592</v>
+        <v>84.58037603278831</v>
       </c>
       <c r="C17" t="n">
-        <v>37.81422086212557</v>
+        <v>41.21090651082814</v>
       </c>
       <c r="D17" t="n">
-        <v>1.361304968759879</v>
+        <v>1.572866457107671</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53670905112293</v>
+        <v>12.2359604588402</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577117757358164</v>
+        <v>0.7501623357083735</v>
       </c>
       <c r="G17" t="n">
-        <v>23.19220703445779</v>
+        <v>26.6733444738627</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14606469491981</v>
+        <v>37.34022510500539</v>
       </c>
       <c r="I17" t="n">
-        <v>2.191007568914129</v>
+        <v>1.319302604086657</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735698598348852</v>
+        <v>4.688514598177332</v>
       </c>
       <c r="K17" t="n">
-        <v>18.0792963077408</v>
+        <v>15.41962396721168</v>
       </c>
       <c r="L17" t="n">
-        <v>44.03351429708896</v>
+        <v>43.32551562189845</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92703146695533</v>
+        <v>99.95604609993826</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.42702525356412</v>
+        <v>85.99254156553103</v>
       </c>
       <c r="C18" t="n">
-        <v>35.65856099817498</v>
+        <v>41.90174836479812</v>
       </c>
       <c r="D18" t="n">
-        <v>1.270754381212531</v>
+        <v>1.574084059156876</v>
       </c>
       <c r="E18" t="n">
-        <v>12.00733861344541</v>
+        <v>12.80300349014542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758292821078007</v>
+        <v>0.7507430583711702</v>
       </c>
       <c r="G18" t="n">
-        <v>21.64951967072693</v>
+        <v>26.80635512931459</v>
       </c>
       <c r="H18" t="n">
-        <v>37.1745498637701</v>
+        <v>37.36913126827194</v>
       </c>
       <c r="I18" t="n">
-        <v>1.827239771593608</v>
+        <v>1.997080445451219</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739330131737543</v>
+        <v>4.692144114819811</v>
       </c>
       <c r="K18" t="n">
-        <v>20.57297474643587</v>
+        <v>14.00745843446898</v>
       </c>
       <c r="L18" t="n">
-        <v>43.70760293403043</v>
+        <v>44.0242753459732</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93913867864129</v>
+        <v>99.9334821452403</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.4611131397868</v>
+        <v>83.3942677264255</v>
       </c>
       <c r="C19" t="n">
-        <v>34.97377667429579</v>
+        <v>39.61328418197299</v>
       </c>
       <c r="D19" t="n">
-        <v>1.236411907016898</v>
+        <v>1.475756380398571</v>
       </c>
       <c r="E19" t="n">
-        <v>11.93678468353778</v>
+        <v>12.2808003135653</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587836798481004</v>
+        <v>0.7512427903895875</v>
       </c>
       <c r="G19" t="n">
-        <v>21.06443565950334</v>
+        <v>25.1318532750438</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19861372580029</v>
+        <v>37.39400602560332</v>
       </c>
       <c r="I19" t="n">
-        <v>1.523685485029767</v>
+        <v>1.665341501490007</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742397999050627</v>
+        <v>4.69526743993492</v>
       </c>
       <c r="K19" t="n">
-        <v>21.53888686021318</v>
+        <v>16.6057322735745</v>
       </c>
       <c r="L19" t="n">
-        <v>43.43657980516899</v>
+        <v>43.72550908763444</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94924333967796</v>
+        <v>99.94452554318192</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.73286572211606</v>
+        <v>80.66432188522641</v>
       </c>
       <c r="C20" t="n">
-        <v>32.47979149626727</v>
+        <v>37.14100434896065</v>
       </c>
       <c r="D20" t="n">
-        <v>1.138523924266779</v>
+        <v>1.372946421104464</v>
       </c>
       <c r="E20" t="n">
-        <v>11.20347867143328</v>
+        <v>11.65667693543503</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592079761054051</v>
+        <v>0.7516738613484399</v>
       </c>
       <c r="G20" t="n">
-        <v>19.39674295711474</v>
+        <v>23.3810190272563</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21941442697502</v>
+        <v>37.41546309679122</v>
       </c>
       <c r="I20" t="n">
-        <v>1.270447915562058</v>
+        <v>1.38858090986319</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745049850658781</v>
+        <v>4.697961633427748</v>
       </c>
       <c r="K20" t="n">
-        <v>24.26713427788393</v>
+        <v>19.33567811477361</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21074962904239</v>
+        <v>43.47705805011324</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9576754031936</v>
+        <v>99.95374051384751</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.81902408253035</v>
+        <v>77.78317708009625</v>
       </c>
       <c r="C21" t="n">
-        <v>36.1863253331972</v>
+        <v>34.47402989971729</v>
       </c>
       <c r="D21" t="n">
-        <v>1.139415214725765</v>
+        <v>1.264933541148012</v>
       </c>
       <c r="E21" t="n">
-        <v>13.21800842286077</v>
+        <v>10.93257326258365</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598023200722431</v>
+        <v>0.7520467918234873</v>
       </c>
       <c r="G21" t="n">
-        <v>21.09742774512979</v>
+        <v>21.54158002029276</v>
       </c>
       <c r="H21" t="n">
-        <v>38.93405164646397</v>
+        <v>37.43402615604377</v>
       </c>
       <c r="I21" t="n">
-        <v>1.921554232826299</v>
+        <v>1.157724859307781</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748764500451519</v>
+        <v>4.700292448896795</v>
       </c>
       <c r="K21" t="n">
-        <v>18.18097591746964</v>
+        <v>22.21682291990377</v>
       </c>
       <c r="L21" t="n">
-        <v>45.56869704513804</v>
+        <v>43.27057548843829</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93599829580488</v>
+        <v>99.96142830805934</v>
       </c>
     </row>
   </sheetData>
